--- a/health-register/screenshots/exports/plan.xlsx
+++ b/health-register/screenshots/exports/plan.xlsx
@@ -977,7 +977,7 @@
         <v/>
       </c>
       <c r="M20" t="str">
-        <v>متأخر التحديث</v>
+        <v>لم يُنفذ</v>
       </c>
     </row>
     <row r="21">
